--- a/data/registro_actual.xlsx
+++ b/data/registro_actual.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Registro" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
   <si>
     <t>Nombre_Facultad</t>
   </si>
@@ -100,24 +100,45 @@
     <t>Facultad_de_Ciencias_de_la_Salud</t>
   </si>
   <si>
+    <t>Facultad_de_Ciencias_Jurídicas</t>
+  </si>
+  <si>
     <t>Especialización en Medicina Crítica y Cuidados Intensivos</t>
   </si>
   <si>
+    <t>Derecho</t>
+  </si>
+  <si>
     <t>Elvia Lucía Sanchez García</t>
   </si>
   <si>
+    <t>Carlos Morales</t>
+  </si>
+  <si>
     <t>Juan Pablo Charry</t>
   </si>
   <si>
+    <t>María Eugenia Nieto</t>
+  </si>
+  <si>
     <t>Temas_Centro_Escritura</t>
   </si>
   <si>
+    <t>APA _(7 ed. 2020)_American_Psychological_Association.</t>
+  </si>
+  <si>
     <t>Alfonso, Virtual</t>
   </si>
   <si>
+    <t>Gonzalo Gallego, Presencial</t>
+  </si>
+  <si>
     <t>Cien años de soledad</t>
   </si>
   <si>
+    <t>Prueba</t>
+  </si>
+  <si>
     <t>Álvaro Agudelo</t>
   </si>
   <si>
@@ -130,16 +151,28 @@
     <t>Sí</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Presencial</t>
   </si>
   <si>
+    <t>Virtual</t>
+  </si>
+  <si>
     <t>Temas_Centro_Escritura | IEEE_(2025)_Institute_of_Electrical_and_Electronics_Engineers</t>
   </si>
   <si>
     <t>Juan Pablo Charry | Diego López, Presencial | Diego Alejandro Soto</t>
   </si>
   <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
     <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>Si</t>
   </si>
   <si>
     <t>alfonso</t>
@@ -504,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -595,67 +628,138 @@
         <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2">
         <v>1053766068</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J2" s="2">
         <v>46073</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="P2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="T2">
         <v>2</v>
       </c>
       <c r="U2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="V2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>123456</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
         <v>40</v>
       </c>
-      <c r="X2" t="s">
+      <c r="J3" s="2">
+        <v>46076</v>
+      </c>
+      <c r="K3" t="s">
         <v>41</v>
       </c>
-      <c r="Z2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" t="s">
+      <c r="L3" t="s">
         <v>42</v>
+      </c>
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3">
+        <v>4</v>
+      </c>
+      <c r="R3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" t="s">
+        <v>50</v>
+      </c>
+      <c r="X3" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data/registro_actual.xlsx
+++ b/data/registro_actual.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Registro" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>Nombre_Facultad</t>
   </si>
@@ -103,24 +103,39 @@
     <t>Facultad_de_Ciencias_Jurídicas</t>
   </si>
   <si>
+    <t>Facultad_de_Ciencias_Contables_Económicas_y_Administrativas</t>
+  </si>
+  <si>
     <t>Especialización en Medicina Crítica y Cuidados Intensivos</t>
   </si>
   <si>
     <t>Derecho</t>
   </si>
   <si>
+    <t>Administración de Empresas</t>
+  </si>
+  <si>
+    <t>1053805543</t>
+  </si>
+  <si>
     <t>Elvia Lucía Sanchez García</t>
   </si>
   <si>
     <t>Carlos Morales</t>
   </si>
   <si>
+    <t>sebas</t>
+  </si>
+  <si>
     <t>Juan Pablo Charry</t>
   </si>
   <si>
     <t>María Eugenia Nieto</t>
   </si>
   <si>
+    <t>Harold Estiven García</t>
+  </si>
+  <si>
     <t>Temas_Centro_Escritura</t>
   </si>
   <si>
@@ -142,9 +157,6 @@
     <t>Álvaro Agudelo</t>
   </si>
   <si>
-    <t>Harold Estiven García</t>
-  </si>
-  <si>
     <t>ok</t>
   </si>
   <si>
@@ -169,10 +181,16 @@
     <t>2026-02-23</t>
   </si>
   <si>
+    <t>2026-02-22</t>
+  </si>
+  <si>
     <t>EN PROCESO</t>
   </si>
   <si>
     <t>Si</t>
+  </si>
+  <si>
+    <t>En proceso</t>
   </si>
   <si>
     <t>alfonso</t>
@@ -537,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -628,67 +646,67 @@
         <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>1053766068</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J2" s="2">
         <v>46073</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="S2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T2">
         <v>2</v>
       </c>
       <c r="U2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="V2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="X2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AA2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -696,70 +714,129 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>123456</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J3" s="2">
         <v>46076</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q3">
         <v>4</v>
       </c>
       <c r="R3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="S3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3" t="s">
+        <v>41</v>
+      </c>
+      <c r="W3" t="s">
+        <v>54</v>
+      </c>
+      <c r="X3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
         <v>36</v>
       </c>
-      <c r="W3" t="s">
-        <v>50</v>
-      </c>
-      <c r="X3" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>38</v>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="2">
+        <v>46075</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W4" t="s">
+        <v>55</v>
+      </c>
+      <c r="X4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/registro_actual.xlsx
+++ b/data/registro_actual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Nombre_Facultad</t>
   </si>
@@ -100,97 +100,46 @@
     <t>Facultad_de_Ciencias_de_la_Salud</t>
   </si>
   <si>
-    <t>Facultad_de_Ciencias_Jurídicas</t>
-  </si>
-  <si>
-    <t>Facultad_de_Ciencias_Contables_Económicas_y_Administrativas</t>
-  </si>
-  <si>
     <t>Especialización en Medicina Crítica y Cuidados Intensivos</t>
   </si>
   <si>
-    <t>Derecho</t>
-  </si>
-  <si>
-    <t>Administración de Empresas</t>
-  </si>
-  <si>
-    <t>1053805543</t>
-  </si>
-  <si>
     <t>Elvia Lucía Sanchez García</t>
   </si>
   <si>
-    <t>Carlos Morales</t>
-  </si>
-  <si>
-    <t>sebas</t>
-  </si>
-  <si>
     <t>Juan Pablo Charry</t>
   </si>
   <si>
-    <t>María Eugenia Nieto</t>
+    <t>Temas_Centro_Escritura</t>
+  </si>
+  <si>
+    <t>Alfonso, Virtual</t>
+  </si>
+  <si>
+    <t>Cien años de soledad</t>
+  </si>
+  <si>
+    <t>Álvaro Agudelo</t>
   </si>
   <si>
     <t>Harold Estiven García</t>
   </si>
   <si>
-    <t>Temas_Centro_Escritura</t>
-  </si>
-  <si>
-    <t>APA _(7 ed. 2020)_American_Psychological_Association.</t>
-  </si>
-  <si>
-    <t>Alfonso, Virtual</t>
-  </si>
-  <si>
-    <t>Gonzalo Gallego, Presencial</t>
-  </si>
-  <si>
-    <t>Cien años de soledad</t>
-  </si>
-  <si>
-    <t>Prueba</t>
-  </si>
-  <si>
-    <t>Álvaro Agudelo</t>
-  </si>
-  <si>
     <t>ok</t>
   </si>
   <si>
     <t>Sí</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Presencial</t>
   </si>
   <si>
-    <t>Virtual</t>
-  </si>
-  <si>
     <t>Temas_Centro_Escritura | IEEE_(2025)_Institute_of_Electrical_and_Electronics_Engineers</t>
   </si>
   <si>
     <t>Juan Pablo Charry | Diego López, Presencial | Diego Alejandro Soto</t>
   </si>
   <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>2026-02-22</t>
-  </si>
-  <si>
     <t>EN PROCESO</t>
-  </si>
-  <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>En proceso</t>
   </si>
   <si>
     <t>alfonso</t>
@@ -555,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -646,197 +595,67 @@
         <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>1053766068</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J2" s="2">
         <v>46073</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="L2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="S2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="T2">
         <v>2</v>
       </c>
       <c r="U2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="V2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="X2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="Z2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="AA2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3">
-        <v>123456</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" s="2">
-        <v>46076</v>
-      </c>
-      <c r="K3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q3">
-        <v>4</v>
-      </c>
-      <c r="R3" t="s">
-        <v>49</v>
-      </c>
-      <c r="S3" t="s">
-        <v>51</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
-      </c>
-      <c r="U3" t="s">
-        <v>41</v>
-      </c>
-      <c r="W3" t="s">
-        <v>54</v>
-      </c>
-      <c r="X3" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="2">
-        <v>46075</v>
-      </c>
-      <c r="K4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S4" t="s">
-        <v>51</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-      <c r="U4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W4" t="s">
-        <v>55</v>
-      </c>
-      <c r="X4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/registro_actual.xlsx
+++ b/data/registro_actual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
   <si>
     <t>Nombre_Facultad</t>
   </si>
@@ -97,33 +97,54 @@
     <t>Historial_Asesor_Metodologico</t>
   </si>
   <si>
+    <t>Detalle_Asesor_Metodologico</t>
+  </si>
+  <si>
     <t>Facultad_de_Ciencias_de_la_Salud</t>
   </si>
   <si>
+    <t>Facultad_de_Ciencias_Contables_Económicas_y_Administrativas</t>
+  </si>
+  <si>
     <t>Especialización en Medicina Crítica y Cuidados Intensivos</t>
   </si>
   <si>
+    <t>Administración de Empresas</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
     <t>Elvia Lucía Sanchez García</t>
   </si>
   <si>
+    <t>Mariana Arredondo</t>
+  </si>
+  <si>
     <t>Juan Pablo Charry</t>
   </si>
   <si>
+    <t>Harold Estiven García</t>
+  </si>
+  <si>
     <t>Temas_Centro_Escritura</t>
   </si>
   <si>
+    <t>APA _(7 ed. 2020)_American_Psychological_Association.</t>
+  </si>
+  <si>
     <t>Alfonso, Virtual</t>
   </si>
   <si>
     <t>Cien años de soledad</t>
   </si>
   <si>
+    <t>La Cándida Heréndida  y su abuela desalmada</t>
+  </si>
+  <si>
     <t>Álvaro Agudelo</t>
   </si>
   <si>
-    <t>Harold Estiven García</t>
-  </si>
-  <si>
     <t>ok</t>
   </si>
   <si>
@@ -133,10 +154,16 @@
     <t>Presencial</t>
   </si>
   <si>
+    <t>Virtual</t>
+  </si>
+  <si>
     <t>Temas_Centro_Escritura | IEEE_(2025)_Institute_of_Electrical_and_Electronics_Engineers</t>
   </si>
   <si>
     <t>Juan Pablo Charry | Diego López, Presencial | Diego Alejandro Soto</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
   </si>
   <si>
     <t>EN PROCESO</t>
@@ -504,10 +531,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,73 +616,135 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>1053766068</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J2" s="2">
         <v>46073</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="P2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="T2">
         <v>2</v>
       </c>
       <c r="U2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="X2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
         <v>41</v>
       </c>
-      <c r="Z2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" t="s">
+      <c r="J3" s="2">
+        <v>46076</v>
+      </c>
+      <c r="K3" t="s">
         <v>42</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3" t="s">
+        <v>38</v>
+      </c>
+      <c r="W3" t="s">
+        <v>49</v>
+      </c>
+      <c r="X3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/registro_actual.xlsx
+++ b/data/registro_actual.xlsx
@@ -14,7 +14,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
+  <si>
+    <t>Cédula</t>
+  </si>
+  <si>
+    <t>Nombre_Usuario</t>
+  </si>
   <si>
     <t>Nombre_Facultad</t>
   </si>
@@ -22,10 +28,7 @@
     <t>Nombre_Programa</t>
   </si>
   <si>
-    <t>Cédula</t>
-  </si>
-  <si>
-    <t>Nombre_Usuario</t>
+    <t>Modalidad del Programa</t>
   </si>
   <si>
     <t>Asesor_Recursos_Académicos</t>
@@ -37,7 +40,10 @@
     <t>Modalidad</t>
   </si>
   <si>
-    <t>Asesor_Metodológico, Modalidad_Asesoría2, Asesor_Metodológico, Modalidad_Asesoría2</t>
+    <t>Asesor_Metodológico</t>
+  </si>
+  <si>
+    <t>Modalidad_Asesoría2</t>
   </si>
   <si>
     <t>Título_Trabajo_Grado</t>
@@ -70,9 +76,6 @@
     <t>Aprobación_Similitud</t>
   </si>
   <si>
-    <t>Modalidad del Programa</t>
-  </si>
-  <si>
     <t>Total_Asesorías</t>
   </si>
   <si>
@@ -100,70 +103,88 @@
     <t>Detalle_Asesor_Metodologico</t>
   </si>
   <si>
+    <t>Elvia Lucía Sanchez García</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
     <t>Facultad_de_Ciencias_de_la_Salud</t>
   </si>
   <si>
-    <t>Facultad_de_Ciencias_Contables_Económicas_y_Administrativas</t>
+    <t>Facultad de Ciencias e Ingenierías</t>
   </si>
   <si>
     <t>Especialización en Medicina Crítica y Cuidados Intensivos</t>
   </si>
   <si>
-    <t>Administración de Empresas</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Elvia Lucía Sanchez García</t>
-  </si>
-  <si>
-    <t>Mariana Arredondo</t>
+    <t>Analítica de Datos</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Virtual</t>
   </si>
   <si>
     <t>Juan Pablo Charry</t>
   </si>
   <si>
+    <t>Juan Pablo Charrly</t>
+  </si>
+  <si>
+    <t>Temas_Centro_Escritura</t>
+  </si>
+  <si>
+    <t>Apa</t>
+  </si>
+  <si>
+    <t>Alfonso</t>
+  </si>
+  <si>
+    <t>Gonzalo Tamayo</t>
+  </si>
+  <si>
+    <t>Cien años de soledad</t>
+  </si>
+  <si>
+    <t>Petroleo en Venezuela</t>
+  </si>
+  <si>
+    <t>Álvaro Agudelo</t>
+  </si>
+  <si>
+    <t>Alvaro Agudelo</t>
+  </si>
+  <si>
     <t>Harold Estiven García</t>
   </si>
   <si>
-    <t>Temas_Centro_Escritura</t>
-  </si>
-  <si>
-    <t>APA _(7 ed. 2020)_American_Psychological_Association.</t>
-  </si>
-  <si>
-    <t>Alfonso, Virtual</t>
-  </si>
-  <si>
-    <t>Cien años de soledad</t>
-  </si>
-  <si>
-    <t>La Cándida Heréndida  y su abuela desalmada</t>
-  </si>
-  <si>
-    <t>Álvaro Agudelo</t>
+    <t>Harold García</t>
+  </si>
+  <si>
+    <t>Si</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
+    <t>bueno</t>
+  </si>
+  <si>
     <t>Sí</t>
   </si>
   <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Virtual</t>
-  </si>
-  <si>
     <t>Temas_Centro_Escritura | IEEE_(2025)_Institute_of_Electrical_and_Electronics_Engineers</t>
   </si>
   <si>
     <t>Juan Pablo Charry | Diego López, Presencial | Diego Alejandro Soto</t>
   </si>
   <si>
-    <t>2026-02-23</t>
+    <t>Gonzalo Tamayo, Virtual</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
   </si>
   <si>
     <t>EN PROCESO</t>
@@ -531,10 +552,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -619,16 +640,19 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:28">
-      <c r="A2" t="s">
-        <v>28</v>
+    <row r="2" spans="1:29">
+      <c r="A2">
+        <v>1053766068</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2">
-        <v>1053766068</v>
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -639,61 +663,64 @@
       <c r="F2" t="s">
         <v>37</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G2" t="s">
         <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="2">
+        <v>41</v>
+      </c>
+      <c r="J2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="2">
         <v>46073</v>
       </c>
-      <c r="K2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>36</v>
+      <c r="M2" t="s">
+        <v>45</v>
       </c>
       <c r="N2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2">
+        <v>50</v>
+      </c>
+      <c r="R2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2">
         <v>0</v>
       </c>
-      <c r="R2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S2" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2">
+      <c r="T2" t="s">
+        <v>52</v>
+      </c>
+      <c r="U2">
         <v>2</v>
       </c>
-      <c r="U2" t="s">
-        <v>47</v>
-      </c>
       <c r="V2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="W2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>57</v>
       </c>
       <c r="AA2" t="s">
-        <v>51</v>
+        <v>37</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
-      <c r="A3" t="s">
-        <v>29</v>
+    <row r="3" spans="1:29">
+      <c r="A3">
+        <v>1053805543</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
@@ -707,44 +734,68 @@
       <c r="F3" t="s">
         <v>38</v>
       </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
       <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="2">
-        <v>46076</v>
+        <v>42</v>
+      </c>
+      <c r="J3" t="s">
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" t="s">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="L3" s="2">
+        <v>46078</v>
+      </c>
+      <c r="M3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" t="s">
+        <v>49</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>51</v>
       </c>
       <c r="R3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3">
+        <v>49</v>
+      </c>
+      <c r="S3">
+        <v>12</v>
+      </c>
+      <c r="T3" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3">
         <v>1</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W3" t="s">
+        <v>55</v>
+      </c>
+      <c r="X3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA3" t="s">
         <v>38</v>
       </c>
-      <c r="W3" t="s">
-        <v>49</v>
-      </c>
-      <c r="X3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>36</v>
+      <c r="AB3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/data/registro_actual.xlsx
+++ b/data/registro_actual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
   <si>
     <t>Cédula</t>
   </si>
@@ -103,24 +103,36 @@
     <t>Detalle_Asesor_Metodologico</t>
   </si>
   <si>
+    <t>1056145563</t>
+  </si>
+  <si>
     <t>Elvia Lucía Sanchez García</t>
   </si>
   <si>
     <t>Francisco</t>
   </si>
   <si>
+    <t>Santi</t>
+  </si>
+  <si>
     <t>Facultad_de_Ciencias_de_la_Salud</t>
   </si>
   <si>
     <t>Facultad de Ciencias e Ingenierías</t>
   </si>
   <si>
+    <t>Facultad_de_Ciencias_Jurídicas</t>
+  </si>
+  <si>
     <t>Especialización en Medicina Crítica y Cuidados Intensivos</t>
   </si>
   <si>
     <t>Analítica de Datos</t>
   </si>
   <si>
+    <t>Especialización en Resolución de Conflictos, Conciliación y Paz</t>
+  </si>
+  <si>
     <t>Presencial</t>
   </si>
   <si>
@@ -133,12 +145,18 @@
     <t>Juan Pablo Charrly</t>
   </si>
   <si>
+    <t>Harold Estiven García</t>
+  </si>
+  <si>
     <t>Temas_Centro_Escritura</t>
   </si>
   <si>
     <t>Apa</t>
   </si>
   <si>
+    <t>APA _(7 ed. 2020)_American_Psychological_Association.</t>
+  </si>
+  <si>
     <t>Alfonso</t>
   </si>
   <si>
@@ -151,21 +169,24 @@
     <t>Petroleo en Venezuela</t>
   </si>
   <si>
+    <t>La casa de muñecas</t>
+  </si>
+  <si>
     <t>Álvaro Agudelo</t>
   </si>
   <si>
     <t>Alvaro Agudelo</t>
   </si>
   <si>
-    <t>Harold Estiven García</t>
-  </si>
-  <si>
     <t>Harold García</t>
   </si>
   <si>
     <t>Si</t>
   </si>
   <si>
+    <t>EN PROCESO</t>
+  </si>
+  <si>
     <t>ok</t>
   </si>
   <si>
@@ -187,7 +208,7 @@
     <t>2026-02-25</t>
   </si>
   <si>
-    <t>EN PROCESO</t>
+    <t>14-03-2026</t>
   </si>
   <si>
     <t>alfonso</t>
@@ -552,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -649,70 +670,70 @@
         <v>1053766068</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L2" s="2">
         <v>46073</v>
       </c>
       <c r="M2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="P2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="R2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="U2">
         <v>2</v>
       </c>
       <c r="V2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="W2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="Y2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AA2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AB2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -720,82 +741,150 @@
         <v>1053805543</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" t="s">
         <v>40</v>
       </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" t="s">
-        <v>36</v>
-      </c>
       <c r="K3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L3" s="2">
         <v>46078</v>
       </c>
       <c r="M3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="N3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="O3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="P3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="S3">
         <v>12</v>
       </c>
       <c r="T3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="U3">
         <v>1</v>
       </c>
       <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="W3" t="s">
-        <v>55</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" s="2">
+        <v>46095</v>
+      </c>
+      <c r="M4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" t="s">
         <v>56</v>
       </c>
-      <c r="Y3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>55</v>
+      <c r="P4" t="s">
+        <v>56</v>
+      </c>
+      <c r="R4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
+        <v>59</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4" t="s">
+        <v>46</v>
+      </c>
+      <c r="X4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/data/registro_actual.xlsx
+++ b/data/registro_actual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
   <si>
     <t>Cédula</t>
   </si>
@@ -103,7 +103,7 @@
     <t>Detalle_Asesor_Metodologico</t>
   </si>
   <si>
-    <t>1056145563</t>
+    <t>1234567</t>
   </si>
   <si>
     <t>Elvia Lucía Sanchez García</t>
@@ -115,6 +115,12 @@
     <t>Santi</t>
   </si>
   <si>
+    <t>Camilo Mendoza</t>
+  </si>
+  <si>
+    <t>Maria Antonia Gómez</t>
+  </si>
+  <si>
     <t>Facultad_de_Ciencias_de_la_Salud</t>
   </si>
   <si>
@@ -124,6 +130,9 @@
     <t>Facultad_de_Ciencias_Jurídicas</t>
   </si>
   <si>
+    <t>Facultad_de_Ciencias_Sociales_Y_Humanas</t>
+  </si>
+  <si>
     <t>Especialización en Medicina Crítica y Cuidados Intensivos</t>
   </si>
   <si>
@@ -133,6 +142,9 @@
     <t>Especialización en Resolución de Conflictos, Conciliación y Paz</t>
   </si>
   <si>
+    <t>Especialización en Comunicación Organizacional</t>
+  </si>
+  <si>
     <t>Presencial</t>
   </si>
   <si>
@@ -172,12 +184,18 @@
     <t>La casa de muñecas</t>
   </si>
   <si>
+    <t>El coronel no tiene quien le escriba</t>
+  </si>
+  <si>
     <t>Álvaro Agudelo</t>
   </si>
   <si>
     <t>Alvaro Agudelo</t>
   </si>
   <si>
+    <t>Wilman Tangarife</t>
+  </si>
+  <si>
     <t>Harold García</t>
   </si>
   <si>
@@ -185,6 +203,9 @@
   </si>
   <si>
     <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>SI</t>
   </si>
   <si>
     <t>ok</t>
@@ -573,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -673,67 +694,67 @@
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" t="s">
         <v>44</v>
       </c>
-      <c r="I2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" t="s">
-        <v>40</v>
-      </c>
       <c r="K2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L2" s="2">
         <v>46073</v>
       </c>
       <c r="M2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="N2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="R2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="U2">
         <v>2</v>
       </c>
       <c r="V2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="W2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="Y2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AA2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AB2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -744,147 +765,241 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L3" s="2">
         <v>46078</v>
       </c>
       <c r="M3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="O3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="Q3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="R3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="S3">
         <v>12</v>
       </c>
       <c r="T3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="U3">
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="W3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="X3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="Y3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="AA3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:29">
-      <c r="A4" t="s">
-        <v>29</v>
+      <c r="A4">
+        <v>1056145563</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L4" s="2">
         <v>46095</v>
       </c>
       <c r="M4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="N4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="O4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="P4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="R4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="U4">
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="X4" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="Y4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5">
+        <v>987654</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
         <v>56</v>
       </c>
-      <c r="AA4" t="s">
-        <v>43</v>
+      <c r="L5" s="2">
+        <v>46097</v>
+      </c>
+      <c r="M5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N5" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" t="s">
+        <v>63</v>
+      </c>
+      <c r="P5" t="s">
+        <v>63</v>
+      </c>
+      <c r="R5" t="s">
+        <v>66</v>
+      </c>
+      <c r="S5">
+        <v>20</v>
+      </c>
+      <c r="T5" t="s">
+        <v>66</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" s="2">
+        <v>46097</v>
+      </c>
+      <c r="M6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N6" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" t="s">
+        <v>63</v>
+      </c>
+      <c r="P6" t="s">
+        <v>63</v>
+      </c>
+      <c r="R6" t="s">
+        <v>66</v>
+      </c>
+      <c r="S6">
+        <v>20</v>
+      </c>
+      <c r="T6" t="s">
+        <v>66</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
